--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136932727</v>
+        <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>99273</v>
+        <v>106406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,38 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Tjugesta, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588662</v>
+        <v>588669</v>
       </c>
       <c r="R3" t="n">
-        <v>6543218</v>
+        <v>6543212</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,15 +885,232 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949586</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136949587</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99990</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Tjugesta, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588692</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6543207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Saga Samuelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949587</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136932727</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla Tjugesta, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>588662</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6543218</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Johan Kjetselberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136932727</t>
         </is>
@@ -908,6 +1120,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>99990</v>
+        <v>99996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>99996</v>
+        <v>99998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>99998</v>
+        <v>99999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>99999</v>
+        <v>100005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106421</v>
+        <v>106425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100005</v>
+        <v>100009</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100009</v>
+        <v>100011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100011</v>
+        <v>100013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100013</v>
+        <v>100026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100026</v>
+        <v>100028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100028</v>
+        <v>100031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100031</v>
+        <v>100041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100041</v>
+        <v>100042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106468</v>
+        <v>106473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100042</v>
+        <v>100047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106473</v>
+        <v>106476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100047</v>
+        <v>100050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106476</v>
+        <v>106482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100050</v>
+        <v>100056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106483</v>
+        <v>106495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100056</v>
+        <v>100068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106495</v>
+        <v>106496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106496</v>
+        <v>106499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100069</v>
+        <v>100072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106499</v>
+        <v>106501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106499</v>
+        <v>106501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100072</v>
+        <v>100073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12929-2023 artfynd.xlsx
+++ b/artfynd/A 12929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932731</v>
       </c>
       <c r="B2" t="n">
-        <v>106501</v>
+        <v>106505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949586</v>
       </c>
       <c r="B3" t="n">
-        <v>106501</v>
+        <v>106505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136949587</v>
       </c>
       <c r="B4" t="n">
-        <v>100073</v>
+        <v>100076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136932727</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
